--- a/data/trans_orig/P34B04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P34B04-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza un entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza un entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,69</t>
+          <t>0,43; 0,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,44</t>
+          <t>0,22; 0,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,25</t>
+          <t>0,06; 0,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,14</t>
+          <t>0,04; 0,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,48</t>
+          <t>0,3; 0,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,5</t>
+          <t>0,32; 0,5</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,46</t>
+          <t>0,22; 0,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,47</t>
+          <t>0,23; 0,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,65</t>
+          <t>0,32; 0,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,04</t>
+          <t>0,0; 0,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,21</t>
+          <t>0,06; 0,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,2</t>
+          <t>0,07; 0,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,27</t>
+          <t>0,13; 0,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,3</t>
+          <t>0,17; 0,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,42</t>
+          <t>0,22; 0,41</t>
         </is>
       </c>
     </row>
@@ -897,37 +897,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,33</t>
+          <t>0,18; 0,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,27</t>
+          <t>0,12; 0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,3</t>
+          <t>0,06; 0,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,16</t>
+          <t>0,03; 0,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,14</t>
+          <t>0,02; 0,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,3</t>
+          <t>0,07; 0,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,26</t>
+          <t>0,14; 0,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,27</t>
+          <t>0,07; 0,27</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,3</t>
+          <t>0,18; 0,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,37</t>
+          <t>0,24; 0,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,08</t>
+          <t>0,01; 0,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,13</t>
+          <t>0,06; 0,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,39</t>
+          <t>0,2; 0,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,44</t>
+          <t>0,2; 0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,16</t>
+          <t>0,09; 0,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,17</t>
+          <t>0,78; 1,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,66</t>
+          <t>0,9; 1,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1252,22 +1252,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,12</t>
+          <t>0,03; 0,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,26</t>
+          <t>0,18; 0,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,34</t>
+          <t>0,23; 0,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,47</t>
+          <t>0,26; 0,48</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,48</t>
+          <t>0,33; 0,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">

--- a/data/trans_orig/P34B04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P34B04-Clase-trans_orig.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,71</t>
+          <t>0,43; 0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,74</t>
+          <t>0,45; 0,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,31</t>
+          <t>0,06; 0,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,13</t>
+          <t>0,04; 0,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,28</t>
+          <t>0,12; 0,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,49</t>
+          <t>0,29; 0,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,28</t>
+          <t>0,15; 0,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,5</t>
+          <t>0,31; 0,49</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,22; 0,46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>0,22; 0,45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,23; 0,45</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,65</t>
+          <t>0,32; 0,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,05</t>
+          <t>0,0; 0,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,21</t>
+          <t>0,06; 0,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,3</t>
+          <t>0,16; 0,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,41</t>
+          <t>0,21; 0,38</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,32</t>
+          <t>0,16; 0,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,31</t>
+          <t>0,21; 0,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,15</t>
+          <t>0,02; 0,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,32</t>
+          <t>0,07; 0,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,21</t>
+          <t>0,1; 0,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,27</t>
+          <t>0,18; 0,37</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,29</t>
+          <t>0,18; 0,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,37</t>
+          <t>0,23; 0,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,45</t>
+          <t>0,23; 0,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1032,22 +1032,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,12</t>
+          <t>0,05; 0,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,2</t>
+          <t>0,12; 0,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,25</t>
+          <t>0,17; 0,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,27</t>
+          <t>0,17; 0,27</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,39</t>
+          <t>0,2; 0,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,34</t>
+          <t>0,17; 0,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,44</t>
+          <t>0,21; 0,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,06</t>
+          <t>0,01; 0,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,24 +1147,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,16</t>
+          <t>0,08; 0,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,18</t>
+          <t>0,09; 0,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,17</t>
+          <t>0,1; 0,2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1227,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,18</t>
+          <t>0,77; 1,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,29</t>
+          <t>0,83; 1,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,68</t>
+          <t>0,93; 1,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1247,27 +1247,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,1</t>
+          <t>0,04; 0,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,13</t>
+          <t>0,04; 0,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,27</t>
+          <t>0,17; 0,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,34</t>
+          <t>0,22; 0,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,48</t>
+          <t>0,25; 0,45</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,47</t>
+          <t>0,39; 0,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,07; 0,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,28</t>
+          <t>0,23; 0,29</t>
         </is>
       </c>
     </row>
